--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_toy-qa-dataset_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_toy-qa-dataset_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.798970588235294</v>
+        <v>0.7065657224905364</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.8581283480925073</v>
       </c>
       <c r="C2" t="n">
-        <v>0.798970588235294</v>
+        <v>0.7065657224905364</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9172972104276498</v>
+        <v>0.8581283480925073</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1845588235294118</v>
+        <v>0.2989165905234304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7056326939277201</v>
+        <v>0.7233311422728601</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.9960187965017622</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9981234211476001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7761904761904762</v>
       </c>
     </row>
   </sheetData>
